--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.70767289119862</v>
+        <v>9.214996844819776</v>
       </c>
       <c r="D2" t="n">
-        <v>56.74155776134674</v>
+        <v>9.220503136218845</v>
       </c>
       <c r="E2" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F2" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.35053422785059</v>
+        <v>5.744461812025721</v>
       </c>
       <c r="D3" t="n">
-        <v>5.977820083346935</v>
+        <v>0.971395763543877</v>
       </c>
       <c r="E3" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F3" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.29289301168177</v>
+        <v>5.085095114398288</v>
       </c>
       <c r="D4" t="n">
-        <v>20.78495161236675</v>
+        <v>3.377554637009597</v>
       </c>
       <c r="E4" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F4" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.43456525840864</v>
+        <v>7.383116854491404</v>
       </c>
       <c r="D5" t="n">
-        <v>25.96678755734163</v>
+        <v>4.219602978068015</v>
       </c>
       <c r="E5" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F5" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.63687589450208</v>
+        <v>7.415992332856588</v>
       </c>
       <c r="D6" t="n">
-        <v>44.98350654126484</v>
+        <v>7.309819812955537</v>
       </c>
       <c r="E6" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F6" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.02928471919308</v>
+        <v>7.317258766868876</v>
       </c>
       <c r="D7" t="n">
-        <v>32.56155755048691</v>
+        <v>5.291253101954123</v>
       </c>
       <c r="E7" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F7" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.05030840801632</v>
+        <v>3.420675116302652</v>
       </c>
       <c r="D8" t="n">
-        <v>21.62271775048525</v>
+        <v>3.513691634453854</v>
       </c>
       <c r="E8" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F8" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>59.98346289116125</v>
+        <v>9.747312719813703</v>
       </c>
       <c r="D9" t="n">
-        <v>43.83882929191777</v>
+        <v>7.123809759936638</v>
       </c>
       <c r="E9" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F9" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>61.83001346840339</v>
+        <v>10.04737718861555</v>
       </c>
       <c r="D10" t="n">
-        <v>53.49269985650263</v>
+        <v>8.692563726681676</v>
       </c>
       <c r="E10" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F10" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.12670746857712</v>
+        <v>7.658089963643782</v>
       </c>
       <c r="D11" t="n">
-        <v>47.21829934238728</v>
+        <v>7.672973643137934</v>
       </c>
       <c r="E11" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F11" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>58.06274646373561</v>
+        <v>9.435196300357038</v>
       </c>
       <c r="D12" t="n">
-        <v>58.32363605140326</v>
+        <v>9.477590858353031</v>
       </c>
       <c r="E12" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F12" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>79.24243031578438</v>
+        <v>12.87689492631496</v>
       </c>
       <c r="D13" t="n">
-        <v>78.57353387565611</v>
+        <v>12.76819925479412</v>
       </c>
       <c r="E13" t="n">
-        <v>14.90412332618382</v>
+        <v>2.421920040504871</v>
       </c>
       <c r="F13" t="n">
-        <v>19.33459191359961</v>
+        <v>3.141871185959937</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
